--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.1</t>
+    <t>2.2.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.2</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
